--- a/site/exports/xjtu-public-health.xlsx
+++ b/site/exports/xjtu-public-health.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,18 +443,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="58.8" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="37.8" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -622,11 +622,119 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>宁玉洁</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>公共卫生学院</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn/jsnr.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1632&amp;wbwbxjtuteacherid=3736</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Partial purposeful professional source sample, not exhaustive biography or school coverage.；Degree labels alone do not prove conferral; award dates and own advisors remain unknown.；Bibliography from official profile only; publisher metadata, full text and original thesis not verified.；Necessary factual extractions and minimal quotations retained, not original full HTTP or complete page snapshots.；No clinical guidance, patient information, contact details or unrelated private biography retained.；University page preserves degree/joint-training labels omitted from college page; omission is not treated as contradiction. Page initial publication timestamp2017 predates later-listed2024 work; it is not treated as date of all profile content. No current status inferred.；Independent review checked retained researcher factual extractions and minimal quotations, not literal full source body or fresh network responses. Publication title is unknown in reviewed consumer view; supported author token/journal/year/volume/pages or article number retained.；来源单位：公共卫生学院／地方病研究所（院系页标签）。本站按“公共卫生学院”归组仅供展示，保留原单位标签；不据此认证法律行政层级、校区或当前任职。</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>吴少伟</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>公共卫生学院</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.xjtu.edu.cn/info/1121/5049.htm</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Partial purposeful professional source sample, not exhaustive biography or school coverage.；Degree labels alone do not prove conferral; award dates and own advisors remain unknown.；Bibliography from official profile only; publisher metadata, full text and original thesis not verified.；Necessary factual extractions and minimal quotations retained, not original full HTTP or complete page snapshots.；No clinical guidance, patient information, contact details or unrelated private biography retained.；Independent review checked retained researcher factual extractions and minimal quotations, not literal full source body or fresh network responses. Publication title is unknown in reviewed consumer view; supported author token/journal/year/volume/pages or article number retained.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -638,13 +746,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="40.59999999999999" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -657,7 +765,7 @@
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="65" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="58.8" customWidth="1" min="17" max="17"/>
+    <col width="65" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
   </cols>
@@ -720,7 +828,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1665,8 +1773,652 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>宁玉洁</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>学士</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>陕西中医药大学</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2005.9</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2010.7</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源institutional_unit_as_source：公共卫生学院</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn/jsnr.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1632&amp;wbwbxjtuteacherid=3736</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>宁玉洁</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2010.9</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2016.9</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源institutional_unit_as_source：医学部公共卫生学院</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn/jsnr.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1632&amp;wbwbxjtuteacherid=3736</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>宁玉洁</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>博士联培</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>澳大利亚悉尼大学</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2014.12</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2015.12</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>Joint-training event itself is not an independent degree award; underlying doctoral conferral remains unknown.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源institutional_unit_as_source：医学院</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn/jsnr.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1632&amp;wbwbxjtuteacherid=3736</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>宁玉洁</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>副教授</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学医学院公共卫生学院</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源role_as_source：副教授；来源institution_as_source：西安交通大学医学院公共卫生学院；来源period_as_source：2020年10月-至今</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn/jsnr.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1632&amp;wbwbxjtuteacherid=3736</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>吴少伟</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>学士</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>北京大学</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2002.9</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2007.7</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>预防医学</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源institutional_unit_as_source：公共卫生学院</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.xjtu.edu.cn/info/1121/5049.htm</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>吴少伟</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>硕士</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>北京大学</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2007.9</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2009.7</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>劳动卫生与环境卫生学</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源institutional_unit_as_source：公共卫生学院</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.xjtu.edu.cn/info/1121/5049.htm</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>吴少伟</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>博士</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>北京大学</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2009.9</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2012.7</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>劳动卫生与环境卫生学</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源institutional_unit_as_source：公共卫生学院</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.xjtu.edu.cn/info/1121/5049.htm</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>吴少伟</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>博士后</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>哈佛医学院附属布莱根与妇女医院（BWH）</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2012.7</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2014.6</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>Nondegree postdoctoral event listed under work history; does not imply another degree.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.xjtu.edu.cn/info/1121/5049.htm</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>吴少伟</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>博士后</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>布朗大学沃伦·阿尔珀特医学院</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2014.7</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2015.6</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>Nondegree postdoctoral event listed under work history; does not imply another degree.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.xjtu.edu.cn/info/1121/5049.htm</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>吴少伟</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>教授</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学公共卫生学院</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源role_as_source：教授；来源institution_as_source：西安交通大学公共卫生学院；来源period_as_source：2020.10至今</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.xjtu.edu.cn/info/1121/5049.htm</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S15"/>
+  <autoFilter ref="A1:S25"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1682,6 +2434,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2116,7 +2878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2307,8 +3069,104 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>宁玉洁</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.xjtu.edu.cn/info/1116/5370.htm</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.xjtu.edu.cn/info/1116/5370.htm</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源person_contribution_role_as_source：Listed author; # meaning unverified, not inferred co-first authorship；来源书目信息（卷）：748；来源书目信息（文章编号）：109785；来源书目信息（selected_author_token_as_source）：Ning Y#</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>吴少伟</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.xjtu.edu.cn/info/1121/5049.htm</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.xjtu.edu.cn/info/1121/5049.htm</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源person_contribution_role_as_source：通讯作者（该页面明确说明*）；来源书目信息（卷）：31；来源书目信息（期）：5；来源书目信息（页码）：1688-1697；来源书目信息（selected_author_token_as_source）：Wu S*</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L5"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -2316,6 +3174,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2327,14 +3189,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30.8" customWidth="1" min="2" max="2"/>
-    <col width="58.8" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="3" max="3"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2524,13 +3386,127 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>宁玉洁</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-xjtu-ningyujie-publichealth-s001-34b757f7d12a</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn/jsnr.jsp?urltype=tree.TreeTempUrl&amp;wbtreeid=1632&amp;wbwbxjtuteacherid=3736</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:50Z</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>宁玉洁</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-xjtu-ningyujie-publichealth-s002-ec97841a0814</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.xjtu.edu.cn/info/1116/5370.htm</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:19:21Z</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>吴少伟</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-xjtu-wushaowei-publichealth-s001-474d6475da68</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>https://sph.xjtu.edu.cn/info/1121/5049.htm</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T07:18:50Z</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>xjtu</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/exports/xjtu-public-health.xlsx
+++ b/site/exports/xjtu-public-health.xlsx
@@ -1875,7 +1875,7 @@
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
@@ -2064,7 +2064,7 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr"/>
@@ -2133,7 +2133,7 @@
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr"/>
@@ -2202,7 +2202,7 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr"/>
